--- a/data/trans_bre/IP16B08-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16B08-Provincia-trans_bre.xlsx
@@ -586,7 +586,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -666,7 +666,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -746,7 +746,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -986,7 +986,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1066,7 +1066,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,11</t>
+          <t>0,0; 69,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 223,68</t>
+          <t>0,0; 224,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-13,95; 7,14</t>
+          <t>-17,01; 6,93</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,54</t>
+          <t>0,0; 22,1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-16,85; 7,62</t>
+          <t>-18,25; 7,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,12</t>
+          <t>0,0; 28,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">

--- a/data/trans_bre/IP16B08-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16B08-Provincia-trans_bre.xlsx
@@ -1199,7 +1199,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,21</t>
+          <t>0,0; 68,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 224,78</t>
+          <t>0,0; 222,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-17,01; 6,93</t>
+          <t>-16,63; 7,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,1</t>
+          <t>0,0; 25,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-18,25; 7,38</t>
+          <t>-17,07; 7,77</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,46</t>
+          <t>0,0; 34,98</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
